--- a/Hardware/production/designators.xlsx
+++ b/Hardware/production/designators.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Saleh\Desktop\Saleh Uni\sem 7\senior year project\Flight Controller\Hardware\production\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF30908B-AADB-493B-A167-4A280DC7867F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6955D716-DD21-4B94-9D75-31130A11B111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="720" windowWidth="19200" windowHeight="11170" xr2:uid="{40A942BE-2DBA-4910-9B0A-4D1B9768C8B0}"/>
+    <workbookView xWindow="1060" yWindow="1060" windowWidth="19200" windowHeight="11170" xr2:uid="{6C3D445B-C5E6-4A0E-B0EE-4B5D0545AE6F}"/>
   </bookViews>
   <sheets>
     <sheet name="designators" sheetId="1" r:id="rId1"/>
@@ -1377,7 +1377,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{076E78EA-93BB-4AC0-9C32-43BE4EB883DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9CA92A4-A51F-4905-AB9A-1D5C6AD3ADE6}">
   <dimension ref="A1:A166"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
